--- a/2025-MLS-projections/Fleet Groups/Fleet_Group_Catch_Index_Fleet_Name.xlsx
+++ b/2025-MLS-projections/Fleet Groups/Fleet_Group_Catch_Index_Fleet_Name.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jon.brodziak\Desktop\2024 WCNPO MLS Rebuilding\2025 MLS projections\Fleet Groups\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{C79E2B89-5AE4-4241-867A-B830E1B8EFEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7363CB7E-0B0A-40A1-A749-8204B66E4073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1509" yWindow="1431" windowWidth="13062" windowHeight="7226"/>
+    <workbookView xWindow="1397" yWindow="257" windowWidth="13766" windowHeight="8186" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fleet_Group_Catch_Index_Fleet_N" sheetId="1" r:id="rId1"/>
@@ -25,9 +25,6 @@
     <t>Fleet Group</t>
   </si>
   <si>
-    <t>Catch Index</t>
-  </si>
-  <si>
     <t>Fleet Name</t>
   </si>
   <si>
@@ -284,12 +281,15 @@
   </si>
   <si>
     <t>"Japanese-drift-net_quarters-2-3_1977-1993"</t>
+  </si>
+  <si>
+    <t>Fishing Fleet SS3 Model Code</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -607,7 +607,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -719,6 +719,111 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -767,8 +872,36 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1123,378 +1256,378 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="10.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.4609375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.15234375" customWidth="1"/>
+    <col min="2" max="2" width="9.61328125" customWidth="1"/>
+    <col min="3" max="3" width="18.15234375" customWidth="1"/>
     <col min="4" max="4" width="49.23046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" s="1" customFormat="1" ht="58.75" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B2" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A3" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B4" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
+      <c r="B5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A6" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D5" t="s">
+      <c r="B6" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A7" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D6" t="s">
+      <c r="B7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A8" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D7" t="s">
+      <c r="C8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A9" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A10" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A11" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A13" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D12" t="s">
+      <c r="C13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A14" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A15" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A16" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A17" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A18" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A19" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A20" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A21" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D14" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" t="s">
-        <v>42</v>
-      </c>
-      <c r="D17" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="B21" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>45</v>
-      </c>
-      <c r="B20" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21" t="s">
-        <v>50</v>
-      </c>
-      <c r="C21" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A22" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D21" t="s">
+      <c r="C22" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
-        <v>11</v>
-      </c>
-      <c r="B22" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A23" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B23" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="D22" t="s">
+      <c r="C23" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A23" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A24" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D23" t="s">
+      <c r="C24" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A24" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" t="s">
-        <v>56</v>
-      </c>
-      <c r="C24" t="s">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A25" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="D24" t="s">
+      <c r="C25" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A25" t="s">
-        <v>3</v>
-      </c>
-      <c r="B25" t="s">
-        <v>58</v>
-      </c>
-      <c r="C25" t="s">
+    <row r="26" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="D25" t="s">
+      <c r="C26" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>86</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A26" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" t="s">
-        <v>60</v>
-      </c>
-      <c r="C26" t="s">
-        <v>61</v>
-      </c>
-      <c r="D26" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>
